--- a/www/download/IND.gross_output.s.mv.rpPE.xlsx
+++ b/www/download/IND.gross_output.s.mv.rpPE.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Petrovic</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>50941.627</t>
+          <t>50941626567.6593</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>51720.053</t>
+          <t>51720052807.8465</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>52258.063</t>
+          <t>52258063269.4126</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>55302.842</t>
+          <t>55302841953.8622</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>60497.2</t>
+          <t>60497200343.1611</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>62014.833</t>
+          <t>62014833288.996</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60970.526</t>
+          <t>60970525560.2388</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>64121.039</t>
+          <t>64121038772.9884</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>62003.921</t>
+          <t>62003920558.2451</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>71861.645</t>
+          <t>71861644562.1808</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>72701.926</t>
+          <t>72701926479.61</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>72587.424</t>
+          <t>72587424053.0337</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>71854.394</t>
+          <t>71854394416.0264</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>72539.402</t>
+          <t>72539402363.0848</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>75175.777</t>
+          <t>75175777131.5601</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>31023.014</t>
+          <t>31023013657.7864</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>31548.244</t>
+          <t>31548244448.373</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>30109.655</t>
+          <t>30109654545.2312</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>32345.77</t>
+          <t>32345770041.1093</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>33683.037</t>
+          <t>33683037179.2133</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>36405.812</t>
+          <t>36405811540.8298</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>37587.38</t>
+          <t>37587379797.0214</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>36835.64</t>
+          <t>36835640024.7653</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>34419.925</t>
+          <t>34419924520.4301</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>38590.589</t>
+          <t>38590588804.3111</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>37315.899</t>
+          <t>37315898959.7218</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>38709.96</t>
+          <t>38709960011.1166</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>37274.658</t>
+          <t>37274658175.5312</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>33228.701</t>
+          <t>33228700533.325</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>29540.14</t>
+          <t>29540139835.1677</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>34258.346</t>
+          <t>34258345506.209</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>32332.815</t>
+          <t>32332814735.2372</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>30972.317</t>
+          <t>30972317048.0592</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>33095.987</t>
+          <t>33095987306.6822</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>34828.761</t>
+          <t>34828760503.0265</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>39440.671</t>
+          <t>39440671070.5347</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>39597.837</t>
+          <t>39597836545.9002</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>38295.009</t>
+          <t>38295008599.3554</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>37869.087</t>
+          <t>37869087187.7886</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>42768.134</t>
+          <t>42768134287.9893</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>41029.709</t>
+          <t>41029709143.8168</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>43059.218</t>
+          <t>43059218129.7648</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>42349.605</t>
+          <t>42349604585.523</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>47482.582</t>
+          <t>47482581760.2586</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>37119.555</t>
+          <t>37119555108.6266</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>15566.506</t>
+          <t>15566505626.3383</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>16025.856</t>
+          <t>16025855894.0156</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>14112.068</t>
+          <t>14112067592.6585</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>13544.427</t>
+          <t>13544426831.3224</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>14101.148</t>
+          <t>14101147793.9476</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>12807.534</t>
+          <t>12807533888.2162</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>11884.29</t>
+          <t>11884289635.8782</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>11648.399</t>
+          <t>11648398574.7808</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>11793.756</t>
+          <t>11793756091.6771</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>13464.248</t>
+          <t>13464247994.5678</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>13418.87</t>
+          <t>13418870469.1361</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>14487.454</t>
+          <t>14487453875.5816</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>14718.719</t>
+          <t>14718718752.1453</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>14995.338</t>
+          <t>14995337787.882</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>15116.734</t>
+          <t>15116734461.6849</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>307738.344</t>
+          <t>307738343648.274</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>307698.487</t>
+          <t>307698486867.264</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>313805.476</t>
+          <t>313805476196.629</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>323565.44</t>
+          <t>323565439568.227</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>339839.239</t>
+          <t>339839238591.357</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>373045.48</t>
+          <t>373045480097.969</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>373945.359</t>
+          <t>373945359273.44</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>384869.944</t>
+          <t>384869944066.489</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>375456.187</t>
+          <t>375456187416.352</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>416069.941</t>
+          <t>416069940686.076</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>425765.046</t>
+          <t>425765045849.805</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>431060.367</t>
+          <t>431060367386.312</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>432785.695</t>
+          <t>432785694740.147</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>443339.686</t>
+          <t>443339685724.248</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>439003.32</t>
+          <t>439003320037.936</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>100119.92</t>
+          <t>100119920052.128</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>100398.828</t>
+          <t>100398827939.168</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>101334.796</t>
+          <t>101334796223.705</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>107433.781</t>
+          <t>107433781345.012</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>115236.393</t>
+          <t>115236393145.56</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>130321.042</t>
+          <t>130321042120.813</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>130704.48</t>
+          <t>130704480111.678</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>125075.84</t>
+          <t>125075839681.258</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>117836.768</t>
+          <t>117836768361.935</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>133428.067</t>
+          <t>133428066515.445</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>134438.458</t>
+          <t>134438458177.998</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>135181.695</t>
+          <t>135181695205.584</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>124772.072</t>
+          <t>124772072222.49</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>121124.715</t>
+          <t>121124714844.981</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>114613.236</t>
+          <t>114613236479.436</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>3246415.694</t>
+          <t>3246415693891.79</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>3356746.804</t>
+          <t>3356746803582.95</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>3438438.184</t>
+          <t>3438438184082.89</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>3506306.448</t>
+          <t>3506306448292.7</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>3560983.267</t>
+          <t>3560983266864.44</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>3625775.264</t>
+          <t>3625775264096.64</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3696018.817</t>
+          <t>3696018816628.53</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3726530.157</t>
+          <t>3726530156859.97</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>3750400.698</t>
+          <t>3750400698480.86</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>4028616.273</t>
+          <t>4028616273399.14</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>4281597.071</t>
+          <t>4281597071087.01</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>4767921.218</t>
+          <t>4767921218043.13</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>4810384.223</t>
+          <t>4810384222658</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>4968183.182</t>
+          <t>4968183181982.41</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>5077747.824</t>
+          <t>5077747823778.29</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1987.551</t>
+          <t>1987551370.0567</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2081.173</t>
+          <t>2081173384.83923</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1900.169</t>
+          <t>1900168638.14717</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1975.928</t>
+          <t>1975927869.99787</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2198.759</t>
+          <t>2198758922.16449</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2314.637</t>
+          <t>2314637158.83423</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2510.471</t>
+          <t>2510471010.29609</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2586.655</t>
+          <t>2586654523.13843</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2461.263</t>
+          <t>2461263108.45974</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2449.79</t>
+          <t>2449790208.47076</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2197.319</t>
+          <t>2197318714.56007</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2198.02</t>
+          <t>2198020050.8686</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>2099.163</t>
+          <t>2099162811.8811</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2595.129</t>
+          <t>2595128867.42997</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>1879.506</t>
+          <t>1879505589.56892</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>50039.039</t>
+          <t>50039039188.2153</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>49923.028</t>
+          <t>49923027970.0733</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>50965.953</t>
+          <t>50965953435.7058</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>51462.464</t>
+          <t>51462464353.6218</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>50804.488</t>
+          <t>50804487848.8159</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>50754.061</t>
+          <t>50754060656.7064</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>51627.599</t>
+          <t>51627598961.1217</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>51431.85</t>
+          <t>51431849931.356</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>46351.287</t>
+          <t>46351286905.9642</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>49954.613</t>
+          <t>49954613416.0912</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>49439.924</t>
+          <t>49439923798.8288</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>51538.766</t>
+          <t>51538766342.7088</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>49743.863</t>
+          <t>49743863223.3319</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>46329.279</t>
+          <t>46329278545.5762</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>39850.702</t>
+          <t>39850702200.5524</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>311127.006</t>
+          <t>311127005730.319</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>285477.224</t>
+          <t>285477224458.872</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>273510.325</t>
+          <t>273510324626.883</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>301832.648</t>
+          <t>301832648252.259</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>312256.955</t>
+          <t>312256954791.826</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>338228.112</t>
+          <t>338228111742.557</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>327069.865</t>
+          <t>327069865464.286</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>316259.751</t>
+          <t>316259750614.534</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>306077.636</t>
+          <t>306077636273.224</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>334419.507</t>
+          <t>334419506523.116</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>321248.819</t>
+          <t>321248818857.671</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>326779.126</t>
+          <t>326779125962.369</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>319580.142</t>
+          <t>319580141724.01</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>279202.824</t>
+          <t>279202824055.131</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>244215.805</t>
+          <t>244215805063.03</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>24059.694</t>
+          <t>24059694094.999</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>23655.559</t>
+          <t>23655558708.8108</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>25403.921</t>
+          <t>25403921327.2653</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>24956.387</t>
+          <t>24956387090.1352</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>24463.319</t>
+          <t>24463319107.1087</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>25941.493</t>
+          <t>25941493303.7652</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>26653.465</t>
+          <t>26653464661.1685</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>26077.47</t>
+          <t>26077470095.7797</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>25144.151</t>
+          <t>25144151252.3217</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>27062.391</t>
+          <t>27062391376.0764</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>26237.148</t>
+          <t>26237147630.6889</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>26285.587</t>
+          <t>26285586873.6134</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>24382.502</t>
+          <t>24382502366.9115</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>22363.346</t>
+          <t>22363345524.3906</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>19710.722</t>
+          <t>19710722314.2717</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>92848.639</t>
+          <t>92848639072.3142</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>95469.692</t>
+          <t>95469692286.1652</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>93592.673</t>
+          <t>93592672560.3688</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>106208.191</t>
+          <t>106208191296.209</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>118618.548</t>
+          <t>118618548103.448</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>136476.001</t>
+          <t>136476001413.811</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>139588.008</t>
+          <t>139588007869.798</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>146939.651</t>
+          <t>146939651439.145</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>140001.942</t>
+          <t>140001942157.937</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>155255.535</t>
+          <t>155255534843.654</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>162274.585</t>
+          <t>162274585363.07</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>166875.496</t>
+          <t>166875495644.687</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>161263.014</t>
+          <t>161263014129.124</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>147618.32</t>
+          <t>147618320492.539</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>123746.969</t>
+          <t>123746969194.524</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>6501.365</t>
+          <t>6501365175.28064</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>6004.703</t>
+          <t>6004703275.67064</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>6095.807</t>
+          <t>6095807080.8171</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>6360.045</t>
+          <t>6360044653.23066</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>6011.231</t>
+          <t>6011231261.88727</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>6600.485</t>
+          <t>6600485104.64699</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>7005.381</t>
+          <t>7005380794.12761</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>7162.568</t>
+          <t>7162567760.17264</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>6836.171</t>
+          <t>6836170837.50784</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>7709.633</t>
+          <t>7709633189.45132</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>7198.861</t>
+          <t>7198861370.89849</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>7139.388</t>
+          <t>7139388091.21153</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>6349.614</t>
+          <t>6349614493.24443</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>5807.128</t>
+          <t>5807127852.00025</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>4969.005</t>
+          <t>4969005065.51056</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>24817.162</t>
+          <t>24817161600.9149</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>24123.017</t>
+          <t>24123016642.8085</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>24066.017</t>
+          <t>24066016710.9816</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>26839.63</t>
+          <t>26839630234.1731</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>29303.06</t>
+          <t>29303059797.1541</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>30574.467</t>
+          <t>30574467425.2533</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>29861.966</t>
+          <t>29861965686.6318</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>29343.03</t>
+          <t>29343029694.0936</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>27653.51</t>
+          <t>27653510490.8875</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>29942.21</t>
+          <t>29942210233.8969</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>30023.663</t>
+          <t>30023662678.1861</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>30482.226</t>
+          <t>30482226254.1676</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>29090.913</t>
+          <t>29090912710.7105</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>26383.277</t>
+          <t>26383277121.9434</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>21300.06</t>
+          <t>21300060156.5705</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>161045.555</t>
+          <t>161045555404.017</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>157786.714</t>
+          <t>157786713971.238</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>148693.647</t>
+          <t>148693646827.089</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>162823.573</t>
+          <t>162823573231.159</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>177784.083</t>
+          <t>177784082745.174</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>191195.046</t>
+          <t>191195046064.632</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>191593.948</t>
+          <t>191593948384.658</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>185011.028</t>
+          <t>185011027980.159</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>174948.928</t>
+          <t>174948927639.204</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>190013.057</t>
+          <t>190013056789.333</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>190153.476</t>
+          <t>190153476054.732</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>188956.062</t>
+          <t>188956061735.101</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>183975.87</t>
+          <t>183975869935.862</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>166667.045</t>
+          <t>166667045047.437</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>151976.513</t>
+          <t>151976513313.475</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>179354.298</t>
+          <t>179354298337.194</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>179282.7</t>
+          <t>179282700315.377</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>180209.172</t>
+          <t>180209172073.938</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>193146.095</t>
+          <t>193146095156.392</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>200262.779</t>
+          <t>200262778873.018</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>209775.851</t>
+          <t>209775851013.975</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>207502.527</t>
+          <t>207502527081.315</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>204672.233</t>
+          <t>204672232707.542</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>188305.92</t>
+          <t>188305920179.614</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>203867.23</t>
+          <t>203867229853.064</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>206265.808</t>
+          <t>206265808358.747</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>204108.473</t>
+          <t>204108472714.402</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>192155.4</t>
+          <t>192155399936.801</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>166797.145</t>
+          <t>166797144779.483</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>157295.436</t>
+          <t>157295435542.821</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>24514.351</t>
+          <t>24514351301.8653</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>25336.893</t>
+          <t>25336892983.0756</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>23839.786</t>
+          <t>23839786475.0995</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>25774.345</t>
+          <t>25774345195.7349</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>26557.504</t>
+          <t>26557503946.7119</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>30597.26</t>
+          <t>30597260251.6996</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>29425.778</t>
+          <t>29425777829.0994</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>29874.692</t>
+          <t>29874692083.6905</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>27790.379</t>
+          <t>27790378631.1524</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>30054.752</t>
+          <t>30054751502.2948</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>29331.06</t>
+          <t>29331060280.9098</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>31480.704</t>
+          <t>31480704026.7286</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>30050.16</t>
+          <t>30050160367.6554</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>29417.77</t>
+          <t>29417769999.4446</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>27128.813</t>
+          <t>27128813119.4059</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>38455.423</t>
+          <t>38455423032.4149</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>37006.423</t>
+          <t>37006423069.7982</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>35569.958</t>
+          <t>35569958007.4201</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>37931.458</t>
+          <t>37931457597.9593</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>42297.756</t>
+          <t>42297755539.6325</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>42381.667</t>
+          <t>42381666902.7367</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>41291.478</t>
+          <t>41291477973.7381</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>40886.585</t>
+          <t>40886584565.1814</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>37758.992</t>
+          <t>37758991610.0418</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>38666.769</t>
+          <t>38666769270.4004</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>37446.849</t>
+          <t>37446849334.3822</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>36801.296</t>
+          <t>36801296193.2299</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>35060.322</t>
+          <t>35060322376.2496</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>30240.039</t>
+          <t>30240038589.344</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>28340.957</t>
+          <t>28340957384.242</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>222204.134</t>
+          <t>222204133805.302</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>235351.5</t>
+          <t>235351500348.716</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>235445.911</t>
+          <t>235445911208.005</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>227321.623</t>
+          <t>227321623129.597</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>262583.538</t>
+          <t>262583537538.348</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>289731.384</t>
+          <t>289731383950.813</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>295815.444</t>
+          <t>295815443569.58</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>311949.758</t>
+          <t>311949757837.31</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>307588.277</t>
+          <t>307588276655.748</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>323061.365</t>
+          <t>323061365041.134</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>281000.46</t>
+          <t>281000460005.816</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>273314.025</t>
+          <t>273314024520.921</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>275167.556</t>
+          <t>275167556259.789</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>273594.09</t>
+          <t>273594090052.275</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>288680.189</t>
+          <t>288680189391.522</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2241634.269</t>
+          <t>2241634268951.45</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2275860.099</t>
+          <t>2275860098527.06</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2357707.616</t>
+          <t>2357707616321.75</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2448896.598</t>
+          <t>2448896597687.93</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2463220.457</t>
+          <t>2463220456616.64</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2680537.496</t>
+          <t>2680537496308.65</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2835940.099</t>
+          <t>2835940099196.88</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2810390.108</t>
+          <t>2810390107769.16</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2850203.933</t>
+          <t>2850203932774.58</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>3067756.9</t>
+          <t>3067756900026.48</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>3072739.598</t>
+          <t>3072739597809.27</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>3039577.467</t>
+          <t>3039577466987.46</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>2861642.026</t>
+          <t>2861642025806.65</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2758825.654</t>
+          <t>2758825654473.71</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2842416.931</t>
+          <t>2842416931060.79</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>14084.179</t>
+          <t>14084179267.1585</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>14552.547</t>
+          <t>14552546829.4878</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>14519.321</t>
+          <t>14519320899.3881</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>15473.925</t>
+          <t>15473924632.0265</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>17565.856</t>
+          <t>17565856252.4853</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>19370.533</t>
+          <t>19370532743.0435</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>19904.162</t>
+          <t>19904161505.3956</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>19081.312</t>
+          <t>19081312388.2765</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>18837.641</t>
+          <t>18837641003.4023</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>21604.858</t>
+          <t>21604857601.9309</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>22364.754</t>
+          <t>22364753875.5906</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>22934.684</t>
+          <t>22934684273.9088</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>22734.117</t>
+          <t>22734117080.2941</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>20073.896</t>
+          <t>20073896230.4431</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>18786.953</t>
+          <t>18786952671.769</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>151173.981</t>
+          <t>151173980585.676</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>151641.898</t>
+          <t>151641897886.29</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>146752.68</t>
+          <t>146752679532.013</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>161111.301</t>
+          <t>161111300871.324</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>171280.484</t>
+          <t>171280483965.738</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>190281.977</t>
+          <t>190281977200.28</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>187423.851</t>
+          <t>187423850815.447</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>186263.727</t>
+          <t>186263726906.635</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>181228.095</t>
+          <t>181228094790.574</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>198654.812</t>
+          <t>198654811981.91</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>196911.453</t>
+          <t>196911452636.234</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>209530.04</t>
+          <t>209530040144.983</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>200118.625</t>
+          <t>200118624605.294</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>174436.567</t>
+          <t>174436566805.424</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>145481.151</t>
+          <t>145481150991.711</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>691286.221</t>
+          <t>691286220609.538</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>662199.823</t>
+          <t>662199823429.589</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>652747.846</t>
+          <t>652747845528.782</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>638330.728</t>
+          <t>638330727561.461</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>671141.781</t>
+          <t>671141781118.243</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>729510.072</t>
+          <t>729510072007.579</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>715154.961</t>
+          <t>715154960682.232</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>680303.627</t>
+          <t>680303626995.328</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>639126.86</t>
+          <t>639126860052.986</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>700043.647</t>
+          <t>700043647100.064</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>686845.557</t>
+          <t>686845557016.441</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>688512.628</t>
+          <t>688512627588.751</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>641538.713</t>
+          <t>641538713240.349</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>634086.919</t>
+          <t>634086919305.62</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>547907.344</t>
+          <t>547907343508.61</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>313607.954</t>
+          <t>313607954194.895</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>313934.637</t>
+          <t>313934636976.934</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>314412.971</t>
+          <t>314412971158.363</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>306350.515</t>
+          <t>306350514661.772</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>336944.24</t>
+          <t>336944240142.293</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>377118.095</t>
+          <t>377118094697.809</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>375027.639</t>
+          <t>375027639310.142</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>379366.923</t>
+          <t>379366923409.078</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>354945.454</t>
+          <t>354945453606.423</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>402247.104</t>
+          <t>402247104290.365</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>391707.432</t>
+          <t>391707431532.438</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>397185.828</t>
+          <t>397185827643.691</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>367699.219</t>
+          <t>367699218839.346</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>360191.912</t>
+          <t>360191912277.384</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>346687.279</t>
+          <t>346687278912.108</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>13478.175</t>
+          <t>13478175149.1408</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>12819.555</t>
+          <t>12819554722.2379</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>11808.238</t>
+          <t>11808237541.0069</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>12909.897</t>
+          <t>12909896824.6557</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>12433.447</t>
+          <t>12433447260.3502</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>13270.845</t>
+          <t>13270844814.6903</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>12909.043</t>
+          <t>12909043370.1813</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>12802.765</t>
+          <t>12802764756.8835</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>12012.113</t>
+          <t>12012113448.2809</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>12392.055</t>
+          <t>12392054711.9801</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>12919.308</t>
+          <t>12919308428.033</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>12481.277</t>
+          <t>12481276694.5957</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>12216.906</t>
+          <t>12216906223.6753</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>12395.375</t>
+          <t>12395374828.9081</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>11001.657</t>
+          <t>11001656615.8814</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1503.492</t>
+          <t>1503492381.5077</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1326.211</t>
+          <t>1326211025.08894</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1292.199</t>
+          <t>1292199166.76607</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1472.363</t>
+          <t>1472363064.47874</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1471.855</t>
+          <t>1471855178.53094</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>1633.386</t>
+          <t>1633385616.04953</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1587.564</t>
+          <t>1587564286.33007</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>1577.221</t>
+          <t>1577221428.06921</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>1540.782</t>
+          <t>1540782141.86808</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>1941.874</t>
+          <t>1941874182.65268</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>1962.309</t>
+          <t>1962309050.12687</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>1946.803</t>
+          <t>1946802687.62966</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>1882.814</t>
+          <t>1882813762.86113</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>1852.728</t>
+          <t>1852728154.39156</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>1860.628</t>
+          <t>1860628411.5313</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>6588.625</t>
+          <t>6588625199.42253</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>6244.284</t>
+          <t>6244283806.98893</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>6246.13</t>
+          <t>6246129938.2276</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>6543.158</t>
+          <t>6543158314.4799</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>6401.117</t>
+          <t>6401116591.1222</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>6052.325</t>
+          <t>6052325320.83864</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>5942.858</t>
+          <t>5942858171.87198</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>5816.19</t>
+          <t>5816190391.20308</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>5603.191</t>
+          <t>5603191293.80965</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>6421.161</t>
+          <t>6421160932.15558</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>6337.062</t>
+          <t>6337061527.41511</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>6665.383</t>
+          <t>6665382758.48846</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>6831.826</t>
+          <t>6831826125.96177</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>6120.095</t>
+          <t>6120094687.92694</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>4658.507</t>
+          <t>4658507309.95222</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>187067.677</t>
+          <t>187067677182.555</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>194621.255</t>
+          <t>194621255249.823</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>200846.964</t>
+          <t>200846963803.756</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>222369.84</t>
+          <t>222369840319.284</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>235866.137</t>
+          <t>235866136747.51</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>255035.455</t>
+          <t>255035455232.108</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>263467.859</t>
+          <t>263467858532.615</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>258263.26</t>
+          <t>258263260080.317</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>240840.246</t>
+          <t>240840246269.159</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>266907.452</t>
+          <t>266907451694.316</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>276439.62</t>
+          <t>276439620344.138</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>269761.796</t>
+          <t>269761795765.904</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>253027.837</t>
+          <t>253027836829.616</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>258184.768</t>
+          <t>258184767900.17</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>249865.246</t>
+          <t>249865246495.031</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>787.624</t>
+          <t>787624029.272906</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>775.415</t>
+          <t>775415400.071434</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>657.844</t>
+          <t>657843926.503165</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>735.589</t>
+          <t>735589072.330446</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>868.891</t>
+          <t>868890713.23994</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>1044.004</t>
+          <t>1044003748.90968</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>847.892</t>
+          <t>847892378.226845</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>864.158</t>
+          <t>864158047.266202</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>847.471</t>
+          <t>847471308.003418</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>864.545</t>
+          <t>864545320.170048</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>808.226</t>
+          <t>808226337.573305</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>887.051</t>
+          <t>887050598.713625</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>836.182</t>
+          <t>836181568.865398</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>840.103</t>
+          <t>840103487.4604</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>752.718</t>
+          <t>752717910.282848</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>64527.654</t>
+          <t>64527653935.5252</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>65672.781</t>
+          <t>65672781086.6787</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>61370.187</t>
+          <t>61370186599.5202</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>70371.434</t>
+          <t>70371433944.2814</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>77114.48</t>
+          <t>77114480338.0871</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>77703.572</t>
+          <t>77703572459.0776</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>80528.964</t>
+          <t>80528963797.0345</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>71028.328</t>
+          <t>71028327998.7374</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>78527.359</t>
+          <t>78527358949.3193</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>85536.651</t>
+          <t>85536650711.472</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>87178.763</t>
+          <t>87178763136.373</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>85907.438</t>
+          <t>85907438287.4952</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>85218.981</t>
+          <t>85218981375.5777</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>83769.716</t>
+          <t>83769715919.027</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>74787.514</t>
+          <t>74787514298.4889</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>129069.536</t>
+          <t>129069535767.412</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>127879</t>
+          <t>127878999794.888</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>125628.267</t>
+          <t>125628266911.649</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>131022.14</t>
+          <t>131022140161.596</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>128451.279</t>
+          <t>128451279331.764</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>133787.201</t>
+          <t>133787200772.714</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>121389.428</t>
+          <t>121389428289.025</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>114245.491</t>
+          <t>114245491386.168</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>106305.957</t>
+          <t>106305957024.706</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>116714.675</t>
+          <t>116714675111.568</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>119353.246</t>
+          <t>119353245761.353</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>122250.464</t>
+          <t>122250463841.314</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>122164.296</t>
+          <t>122164296354.991</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>116532.112</t>
+          <t>116532111970.583</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>109310.292</t>
+          <t>109310292149.799</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>25026.464</t>
+          <t>25026464078.403</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>24396.02</t>
+          <t>24396020228.7963</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>22448.514</t>
+          <t>22448514346.0178</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>24594.121</t>
+          <t>24594121165.5266</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>25338.936</t>
+          <t>25338936353.5467</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>28348.91</t>
+          <t>28348910493.2032</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>28633.456</t>
+          <t>28633455709.6609</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>27691.654</t>
+          <t>27691654434.4998</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>26444.07</t>
+          <t>26444069870.3533</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>29269.044</t>
+          <t>29269044301.0462</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>28118.264</t>
+          <t>28118264306.7387</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>28295.032</t>
+          <t>28295031781.9657</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>28217.022</t>
+          <t>28217021531.9753</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>28422.789</t>
+          <t>28422788949.7459</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>22826.136</t>
+          <t>22826135569.0302</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>46884.51</t>
+          <t>46884509622.1492</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>48167.49</t>
+          <t>48167490373.5687</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>41698.969</t>
+          <t>41698968581.2867</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>38831.465</t>
+          <t>38831465239.8755</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>45939.979</t>
+          <t>45939978678.2179</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>45303.611</t>
+          <t>45303610786.5075</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>45810.179</t>
+          <t>45810179364.448</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>43040.9</t>
+          <t>43040899854.1881</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>42001.43</t>
+          <t>42001430049.2288</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>43286.998</t>
+          <t>43286997925.3067</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>42701.99</t>
+          <t>42701989752.0176</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>43040.439</t>
+          <t>43040439000.0891</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>42568.018</t>
+          <t>42568017575.3941</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>42574.364</t>
+          <t>42574364181.2059</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>41297.765</t>
+          <t>41297765108.6464</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>697457.408</t>
+          <t>697457407740.665</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>685099.595</t>
+          <t>685099594682.698</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>646009.994</t>
+          <t>646009994493.726</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>639755.017</t>
+          <t>639755017295.614</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>611208.761</t>
+          <t>611208761444.626</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>654011.62</t>
+          <t>654011619695.408</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>674253.18</t>
+          <t>674253179641.755</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>652181.575</t>
+          <t>652181574645.847</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>596907.594</t>
+          <t>596907593997.419</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>626356.353</t>
+          <t>626356353126.73</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>611759.613</t>
+          <t>611759612594.587</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>585352.967</t>
+          <t>585352967048.226</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>567114.859</t>
+          <t>567114858515.015</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>544534.115</t>
+          <t>544534114543.604</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>535024.932</t>
+          <t>535024932377.459</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>20356.642</t>
+          <t>20356641893.321</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>20265.635</t>
+          <t>20265635038.9856</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>18819.235</t>
+          <t>18819235085.6573</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>19322.864</t>
+          <t>19322863919.6358</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>18982.81</t>
+          <t>18982810120.2151</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>19336.343</t>
+          <t>19336342960.1499</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>19533.702</t>
+          <t>19533701642.3275</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>18570.274</t>
+          <t>18570274250.5242</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>17316.93</t>
+          <t>17316930464.8739</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>18516.497</t>
+          <t>18516497348.449</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>18929.441</t>
+          <t>18929441459.2554</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>19395.346</t>
+          <t>19395345533.7334</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>20028.687</t>
+          <t>20028687367.8549</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>19644.05</t>
+          <t>19644050083.9112</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>18948.879</t>
+          <t>18948878891.0956</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>8249.908</t>
+          <t>8249908314.28241</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>7862.08</t>
+          <t>7862079774.51289</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>7439.6</t>
+          <t>7439600368.50338</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>7883.228</t>
+          <t>7883228352.0101</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>8204.902</t>
+          <t>8204902283.17411</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>8922.885</t>
+          <t>8922884963.92352</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>8681.047</t>
+          <t>8681047249.26061</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>8675.813</t>
+          <t>8675813125.34187</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>8497.866</t>
+          <t>8497865797.48809</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>9092.597</t>
+          <t>9092597485.77229</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>8902.258</t>
+          <t>8902258098.93946</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>9025.528</t>
+          <t>9025527702.52133</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>8889.506</t>
+          <t>8889506195.3117</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>9125.599</t>
+          <t>9125598948.93228</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>8155.485</t>
+          <t>8155484701.20254</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>34273.401</t>
+          <t>34273400749.5897</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>32948.115</t>
+          <t>32948115185.8231</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>32283.016</t>
+          <t>32283016185.3179</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>35274.667</t>
+          <t>35274666684.6525</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>37161.669</t>
+          <t>37161669229.8929</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>42476.334</t>
+          <t>42476334473.844</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>41001.389</t>
+          <t>41001389070.6717</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>40001.727</t>
+          <t>40001727193.1821</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>37706.901</t>
+          <t>37706901159.2492</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>41073.006</t>
+          <t>41073005925.5847</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>41256.128</t>
+          <t>41256127799.2523</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>41022.289</t>
+          <t>41022289055.2101</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>40314.025</t>
+          <t>40314024870.9921</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>35730.33</t>
+          <t>35730330395.0061</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>30937.978</t>
+          <t>30937978496.6967</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>92496.74</t>
+          <t>92496740086.6068</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>95559.092</t>
+          <t>95559091773.0407</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>102783.186</t>
+          <t>102783186260.431</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>106032.283</t>
+          <t>106032283252.726</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>111602.01</t>
+          <t>111602009848.561</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>121078.454</t>
+          <t>121078454316.091</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>115018.954</t>
+          <t>115018953577.674</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>117802.655</t>
+          <t>117802655296.021</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>119857.588</t>
+          <t>119857588245.86</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>129861.038</t>
+          <t>129861037917.719</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>134987.088</t>
+          <t>134987088464.778</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>134545.485</t>
+          <t>134545484966.583</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>131133.347</t>
+          <t>131133346735.284</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>132863.277</t>
+          <t>132863277003.407</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>115298.183</t>
+          <t>115298182841.879</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>96538.87</t>
+          <t>96538870442.9911</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>94571.219</t>
+          <t>94571218912.0802</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>95177.864</t>
+          <t>95177864149.0453</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>99399.244</t>
+          <t>99399244434.2519</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>104905.824</t>
+          <t>104905824245.251</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>119342.085</t>
+          <t>119342085418.854</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>110202.333</t>
+          <t>110202332815.032</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>116809.618</t>
+          <t>116809618241.116</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>112796.822</t>
+          <t>112796821925.024</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>131576.839</t>
+          <t>131576839363.946</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>127575.146</t>
+          <t>127575146245.732</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>128997.743</t>
+          <t>128997742573.66</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>122389.171</t>
+          <t>122389171322.259</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>118966.952</t>
+          <t>118966952021.08</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>103853.038</t>
+          <t>103853038430.397</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>990444.396</t>
+          <t>990444395975.421</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>982619.832</t>
+          <t>982619832267.382</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>997674.002</t>
+          <t>997674002138.996</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>1072753.088</t>
+          <t>1072753087766</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>1124428.806</t>
+          <t>1124428805592.74</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>1229990.832</t>
+          <t>1229990832183.71</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>1187012.223</t>
+          <t>1187012223191.09</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>1128444.633</t>
+          <t>1128444633235.21</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>1030345.953</t>
+          <t>1030345952584.24</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>1139232.727</t>
+          <t>1139232726778.18</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>1149891.424</t>
+          <t>1149891423840.09</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>1148270.34</t>
+          <t>1148270340090.35</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>1057135.784</t>
+          <t>1057135784115.81</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>1010457.318</t>
+          <t>1010457318328.02</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>882530.688</t>
+          <t>882530687966.508</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>5975269.746</t>
+          <t>5975269745779.29</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>6107806.961</t>
+          <t>6107806961107.66</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>6393716.108</t>
+          <t>6393716108140.89</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>6797631.938</t>
+          <t>6797631937695.42</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>6967075.503</t>
+          <t>6967075503497.38</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>7542235.77</t>
+          <t>7542235770013.23</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>7901946.33</t>
+          <t>7901946329939.27</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>8170132.522</t>
+          <t>8170132522425.54</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>7876040.723</t>
+          <t>7876040722742.23</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>8689930.446</t>
+          <t>8689930446002.05</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>8805473.698</t>
+          <t>8805473697927</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>9031595.973</t>
+          <t>9031595972765.15</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>8633809.145</t>
+          <t>8633809144937.26</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>8534617.856</t>
+          <t>8534617855825.14</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>8994481.035</t>
+          <t>8994481035458.43</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>16724825.139</t>
+          <t>16724825138999.3</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>16944793.258</t>
+          <t>16944793257770</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>17332364.649</t>
+          <t>17332364649007.9</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>18095292.486</t>
+          <t>18095292486320.7</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>18589920.288</t>
+          <t>18589920288445.6</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>19930772.907</t>
+          <t>19930772907320.1</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>20452871.729</t>
+          <t>20452871729375.1</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>20602925.78</t>
+          <t>20602925780070.3</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>20038633.778</t>
+          <t>20038633777858.4</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>21876537.028</t>
+          <t>21876537028336.5</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>22194247.331</t>
+          <t>22194247330559</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>22876148.503</t>
+          <t>22876148502905</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>22070568.991</t>
+          <t>22070568990866.1</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>21802155.492</t>
+          <t>21802155492244.3</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>22004281.605</t>
+          <t>22004281605345.5</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>gross_output.s.mv</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Petrovic</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpPE</t>
